--- a/excel_routes/route_CCE_YNB_threats.xlsx
+++ b/excel_routes/route_CCE_YNB_threats.xlsx
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4797</v>
+        <v>5593</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5541</v>
+        <v>7946</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-744</v>
+        <v>-2353</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-180</t>
+          <t>Nile Air NP-103</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4797</v>
+        <v>4832</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5541</v>
+        <v>7946</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-744</v>
+        <v>-3114</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -608,9 +608,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -622,12 +622,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -636,13 +636,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4826</v>
+        <v>7298</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5541</v>
+        <v>10708</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-715</v>
+        <v>-3410</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -653,9 +653,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4826</v>
+        <v>9412</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5541</v>
+        <v>10708</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-715</v>
+        <v>-1296</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -712,12 +712,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>4826</v>
+        <v>9412</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8108</v>
+        <v>10159</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3282</v>
+        <v>-747</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -743,9 +743,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4826</v>
+        <v>7918</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8108</v>
+        <v>8665</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-3282</v>
+        <v>-747</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -788,9 +788,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4826</v>
+        <v>8707</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7687</v>
+        <v>10159</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-2861</v>
+        <v>-1452</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -833,9 +833,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,12 +847,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SM-961</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4826</v>
+        <v>7918</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7687</v>
+        <v>8665</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-2861</v>
+        <v>-747</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -878,9 +878,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,12 +892,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07-APR-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -906,13 +906,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6663</v>
+        <v>7918</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7687</v>
+        <v>10159</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1024</v>
+        <v>-2241</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07-APR-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6663</v>
+        <v>7298</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7687</v>
+        <v>7946</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1024</v>
+        <v>-648</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -982,12 +982,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>17-APR-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6663</v>
+        <v>7918</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7687</v>
+        <v>10159</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1024</v>
+        <v>-2241</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>17-APR-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6663</v>
+        <v>7298</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>7687</v>
+        <v>8665</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1024</v>
+        <v>-1367</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1072,12 +1072,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1086,22 +1086,22 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9385</v>
+        <v>7298</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11335</v>
+        <v>8242</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1950</v>
+        <v>-944</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9385</v>
+        <v>7298</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11335</v>
+        <v>7946</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1950</v>
+        <v>-648</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7898</v>
+        <v>7298</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>9609</v>
+        <v>7946</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1711</v>
+        <v>-648</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1207,12 +1207,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SM-447</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7898</v>
+        <v>7298</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>9609</v>
+        <v>7946</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-1711</v>
+        <v>-648</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1252,12 +1252,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7281</v>
+        <v>7918</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7393</v>
+        <v>7946</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-112</v>
+        <v>-28</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1297,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7393</v>
+        <v>7946</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-112</v>
+        <v>-648</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1342,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1356,13 +1356,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>9609</v>
+        <v>8242</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-2328</v>
+        <v>-944</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1387,12 +1387,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SM-447</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7281</v>
+        <v>7918</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>9609</v>
+        <v>8242</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-2328</v>
+        <v>-324</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1432,12 +1432,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1446,13 +1446,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7281</v>
+        <v>10102</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>7393</v>
+        <v>11300</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-112</v>
+        <v>-1198</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1477,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>7281</v>
+        <v>10102</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>7393</v>
+        <v>11300</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-112</v>
+        <v>-1198</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1522,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7281</v>
+        <v>10807</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>9609</v>
+        <v>11300</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-2328</v>
+        <v>-493</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1567,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7281</v>
+        <v>10807</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>9609</v>
+        <v>11906</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-2328</v>
+        <v>-1099</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
@@ -1612,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7281</v>
+        <v>10807</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>7393</v>
+        <v>11300</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-112</v>
+        <v>-493</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>30</v>
@@ -1657,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>7281</v>
+        <v>10102</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>7393</v>
+        <v>11300</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-112</v>
+        <v>-1198</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>30</v>
@@ -1702,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>7281</v>
+        <v>10102</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>9609</v>
+        <v>11300</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-2328</v>
+        <v>-1198</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>30</v>
@@ -1747,12 +1747,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SM-447</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>7281</v>
+        <v>10102</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>9609</v>
+        <v>11300</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-2328</v>
+        <v>-1198</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>30</v>
@@ -1792,12 +1792,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7393</v>
+        <v>7946</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-112</v>
+        <v>-648</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>30</v>
@@ -1837,7 +1837,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>7393</v>
+        <v>7946</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-112</v>
+        <v>-648</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>30</v>
@@ -1882,7 +1882,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1896,13 +1896,13 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>9609</v>
+        <v>7946</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-2328</v>
+        <v>-648</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>30</v>
@@ -1927,12 +1927,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SM-447</t>
+          <t>SM-441</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1941,13 +1941,13 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>9609</v>
+        <v>7946</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-2328</v>
+        <v>-648</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>30</v>
@@ -1972,12 +1972,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SM-441</t>
+          <t>SM-447</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1986,13 +1986,13 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>7393</v>
+        <v>7946</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-112</v>
+        <v>-648</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>30</v>
@@ -2017,7 +2017,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>29-SEP-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>7281</v>
+        <v>7298</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>7393</v>
+        <v>7946</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-112</v>
+        <v>-648</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>30</v>
